--- a/site/data/downloads/fx_monthly.xlsx
+++ b/site/data/downloads/fx_monthly.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1963,6 +1963,31 @@
         <v>1.1594</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1358.995</v>
+      </c>
+      <c r="C62" t="n">
+        <v>869.521</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1567.1315</v>
+      </c>
+      <c r="E62" t="n">
+        <v>118.9347</v>
+      </c>
+      <c r="F62" t="n">
+        <v>156.2539</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.1531</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1974,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3523,6 +3548,31 @@
         <v>1.1617</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1358.4</v>
+      </c>
+      <c r="C62" t="n">
+        <v>863.16</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1540.29</v>
+      </c>
+      <c r="E62" t="n">
+        <v>120.33</v>
+      </c>
+      <c r="F62" t="n">
+        <v>157.18</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_monthly.xlsx
+++ b/site/data/downloads/fx_monthly.xlsx
@@ -1979,13 +1979,13 @@
         <v>1567.1315</v>
       </c>
       <c r="E62" t="n">
-        <v>118.9347</v>
+        <v>119.2152</v>
       </c>
       <c r="F62" t="n">
-        <v>156.2539</v>
+        <v>156.4171</v>
       </c>
       <c r="G62" t="n">
-        <v>1.1531</v>
+        <v>1.1505</v>
       </c>
     </row>
   </sheetData>
@@ -3564,13 +3564,13 @@
         <v>1540.29</v>
       </c>
       <c r="E62" t="n">
-        <v>120.33</v>
+        <v>120.9693</v>
       </c>
       <c r="F62" t="n">
-        <v>157.18</v>
+        <v>157.25</v>
       </c>
       <c r="G62" t="n">
-        <v>1.14</v>
+        <v>1.1345</v>
       </c>
     </row>
   </sheetData>
